--- a/data/trans_orig/IP19C02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C02-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46381</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53229</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48695</t>
+          <t>48698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>92867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>101254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>35156</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40037</t>
+          <t>40035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27994</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34978</t>
+          <t>34563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65161</t>
+          <t>65379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73731</t>
+          <t>73745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48799</t>
+          <t>49264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83367</t>
+          <t>83342</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87848</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84475</t>
+          <t>83546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93558</t>
+          <t>93551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87405</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94254</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174544</t>
+          <t>173793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185627</t>
+          <t>185810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43883</t>
+          <t>43505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51485</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59138</t>
+          <t>58929</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66853</t>
+          <t>67117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105985</t>
+          <t>105493</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>116871</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35048</t>
+          <t>35017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>67763</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73826</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55962</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>290941</t>
+          <t>290830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>306698</t>
+          <t>306191</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310943</t>
+          <t>312012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326434</t>
+          <t>326394</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608824</t>
+          <t>607716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629114</t>
+          <t>628829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10054</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>42581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>47672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38178</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75907</t>
+          <t>75458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85150</t>
+          <t>84616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46891</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>44891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90437</t>
+          <t>90538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98542</t>
+          <t>98468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>37884</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>34301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39163</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74313</t>
+          <t>75110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80848</t>
+          <t>80751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77312</t>
+          <t>76761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85908</t>
+          <t>85495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94595</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166399</t>
+          <t>165561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179287</t>
+          <t>179189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74433</t>
+          <t>74099</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>80787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65890</t>
+          <t>65664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72423</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143093</t>
+          <t>142800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152084</t>
+          <t>152105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>24282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>32810</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>54774</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>61133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308121</t>
+          <t>308018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>322557</t>
+          <t>321916</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312467</t>
+          <t>312580</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>327724</t>
+          <t>327655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>625269</t>
+          <t>625459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>646250</t>
+          <t>645487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38283</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46817</t>
+          <t>46760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72050</t>
+          <t>72185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83513</t>
+          <t>84154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40954</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50296</t>
+          <t>50849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84435</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98132</t>
+          <t>97463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29692</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51466</t>
+          <t>51662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60307</t>
+          <t>60885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>28643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96196</t>
+          <t>95900</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75040</t>
+          <t>76146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89581</t>
+          <t>89531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162742</t>
+          <t>162615</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182058</t>
+          <t>181992</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>25125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41724</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48711</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59476</t>
+          <t>59612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49355</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62106</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101024</t>
+          <t>101266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117113</t>
+          <t>118124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>44457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55174</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52474</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76550</t>
+          <t>75993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54971</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79762</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113856</t>
+          <t>114743</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149223</t>
+          <t>150367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266193</t>
+          <t>266750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>290269</t>
+          <t>290168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>268719</t>
+          <t>268476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>293510</t>
+          <t>293008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>542001</t>
+          <t>540857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577368</t>
+          <t>576481</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>36659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58683</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43756</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57304</t>
+          <t>57956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59352</t>
+          <t>59431</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>75900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109181</t>
+          <t>109120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129803</t>
+          <t>129939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36594</t>
+          <t>36388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>48817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44566</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57971</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85617</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>103834</t>
+          <t>102972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,68%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>13565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>14777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29602</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48604</t>
+          <t>49411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34638</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25962</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48139</t>
+          <t>48820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76221</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>76047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92854</t>
+          <t>92942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79647</t>
+          <t>79981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>102083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162218</t>
+          <t>162961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190300</t>
+          <t>189619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22129</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45326</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>39481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>65880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>42439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57874</t>
+          <t>58703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81071</t>
+          <t>81979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>105818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>131170</t>
+          <t>132217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13643</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32560</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>50086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31222</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>15881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29077</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39460</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,42%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97962</t>
+          <t>97860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130127</t>
+          <t>129801</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130012</t>
+          <t>130820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>172178</t>
+          <t>173527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>239240</t>
+          <t>240376</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289143</t>
+          <t>289330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256686</t>
+          <t>257012</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>288851</t>
+          <t>288953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>306487</t>
+          <t>305138</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>348653</t>
+          <t>347845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>576335</t>
+          <t>576148</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626238</t>
+          <t>625102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
